--- a/个人随机用药记录.xlsx
+++ b/个人随机用药记录.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yanherdon/Desktop/research/研究计划/量化交易/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yanherdon/Documents/GitHub/RandomizedTrialDataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F07653B-3515-B740-A417-6DFC180E5D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6545B7F2-17F0-8A44-BA19-77B49FCE8588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4120" yWindow="1280" windowWidth="24560" windowHeight="16020" xr2:uid="{22CFECBE-84C1-3F46-83A5-9CD55B752173}"/>
   </bookViews>
@@ -74,10 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新泰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>长兴牌锌硒片（1000099443808）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,6 +99,10 @@
   </si>
   <si>
     <t>服用维生素B(life extention)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -523,13 +523,13 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -547,13 +547,13 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
         <v>14</v>
-      </c>
-      <c r="L1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -576,14 +576,14 @@
       </c>
       <c r="C3" s="2">
         <f ca="1">NOW()</f>
-        <v>45820.731864699075</v>
+        <v>45923.631167245374</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()</f>
-        <v>45820.731864699075</v>
+        <v>45923.631167245374</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1001,14 +1001,14 @@
       </c>
       <c r="C23" s="2">
         <f ca="1">NOW()</f>
-        <v>45820.731864699075</v>
+        <v>45923.631167245374</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" s="2">
         <f ca="1">NOW()</f>
-        <v>45820.731864699075</v>
+        <v>45923.631167245374</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2133,7 +2133,7 @@
         <v>45675.926698379626</v>
       </c>
       <c r="J75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K75" s="2">
         <v>45675.926940972226</v>
@@ -2255,7 +2255,7 @@
         <v>45682.726164814812</v>
       </c>
       <c r="J82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K82" s="2">
         <v>45682.391944444447</v>
@@ -2324,7 +2324,7 @@
         <v>45685.730102546295</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -2436,7 +2436,7 @@
         <v>45696.77559571759</v>
       </c>
       <c r="J96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K96" s="2">
         <v>45696.77559571759</v>
@@ -2459,7 +2459,7 @@
         <v>45697.92226053241</v>
       </c>
       <c r="J97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K97" s="2">
         <v>45697.422256944446</v>
@@ -2529,7 +2529,7 @@
         <v>45702</v>
       </c>
       <c r="J102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K102" s="2">
         <v>45702.840266203704</v>
@@ -2557,7 +2557,7 @@
         <v>45704</v>
       </c>
       <c r="J104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K104" s="2">
         <v>45704.465266203704</v>
@@ -2700,7 +2700,7 @@
         <v>45717</v>
       </c>
       <c r="J117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -2727,7 +2727,7 @@
         <v>45720</v>
       </c>
       <c r="J120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -2743,7 +2743,7 @@
         <v>45722</v>
       </c>
       <c r="J122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -2756,7 +2756,7 @@
         <v>45724</v>
       </c>
       <c r="J124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:11">
